--- a/Documentacion/Historias_de_Usuario_MVP_SportMatch.xlsx
+++ b/Documentacion/Historias_de_Usuario_MVP_SportMatch.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elcacas/Desktop/soportmach/CAPSTONE_PDP/Documentacion/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D161D8B8-B094-1549-AFF8-F620BB14A31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="620" yWindow="-15360" windowWidth="27320" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Historias de Usuario" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Resumen por Épica" sheetId="2" r:id="rId5"/>
+    <sheet name="Historias de Usuario" sheetId="1" r:id="rId1"/>
+    <sheet name="Resumen por Épica" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="LjcLX9Mvc+GwNKeJvA+iUtp2bg15Df9TA47dd4JJNHc="/>
@@ -17,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="303">
   <si>
     <t>ID</t>
   </si>
@@ -962,48 +971,100 @@
 - Cada pago muestra al deportista o club, el monto, el código de autorización y la suscripción asociada.
 - No puedo modificar manualmente el resultado de un pago.</t>
   </si>
+  <si>
+    <t>HU-58</t>
+  </si>
+  <si>
+    <t>Como Usuario en un chat deportivo, necesito compartir mi ubicación o imágenes del punto de encuentro, para facilitar la llegada y coordinación física de los eventos deportivos.</t>
+  </si>
+  <si>
+    <t>Permite adjuntar imágenes del recinto/cancha y enviar punto geolocalizado.</t>
+  </si>
+  <si>
+    <t>HU-59</t>
+  </si>
+  <si>
+    <t>Permite silenciar notificaciones de un chat grupal o individual. · Permite bloquear a un usuario, impidiendo futuros mensajes y contacto directo.</t>
+  </si>
+  <si>
+    <t>HU-60</t>
+  </si>
+  <si>
+    <t>Genera alerta push inmediata en el dispositivo cuando la app está en segundo plano o cerrada. · Notificación en tiempo real dentro de la app cuando el usuario está activo.</t>
+  </si>
+  <si>
+    <t>compartir archivos por el chat</t>
+  </si>
+  <si>
+    <t>silenciar usuarios/bloqueo de cuenta</t>
+  </si>
+  <si>
+    <t>Aviso de segundo plano</t>
+  </si>
+  <si>
+    <t>ya</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri (Cuerpo)"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1011,7 +1072,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1056,8 +1117,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
@@ -1071,80 +1138,93 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1334,31 +1414,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.0"/>
-    <col customWidth="1" min="2" max="2" width="12.0"/>
-    <col customWidth="1" min="3" max="3" width="34.0"/>
-    <col customWidth="1" min="4" max="4" width="10.0"/>
-    <col customWidth="1" min="5" max="5" width="20.0"/>
-    <col customWidth="1" min="6" max="6" width="16.0"/>
-    <col customWidth="1" min="7" max="7" width="34.0"/>
-    <col customWidth="1" min="8" max="8" width="40.0"/>
-    <col customWidth="1" min="9" max="9" width="10.0"/>
-    <col customWidth="1" min="10" max="10" width="9.0"/>
-    <col customWidth="1" min="11" max="11" width="10.0"/>
-    <col customWidth="1" min="12" max="26" width="8.71"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +1473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" ht="65" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -1422,13 +1502,13 @@
         <v>34</v>
       </c>
       <c r="J2" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
@@ -1457,13 +1537,13 @@
         <v>55</v>
       </c>
       <c r="J3" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" ht="78" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
@@ -1492,13 +1572,13 @@
         <v>34</v>
       </c>
       <c r="J4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>61</v>
       </c>
@@ -1527,13 +1607,13 @@
         <v>55</v>
       </c>
       <c r="J5" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" ht="39" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>65</v>
       </c>
@@ -1562,13 +1642,13 @@
         <v>34</v>
       </c>
       <c r="J6" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>70</v>
       </c>
@@ -1597,13 +1677,13 @@
         <v>34</v>
       </c>
       <c r="J7" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" ht="39" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -1632,13 +1712,13 @@
         <v>34</v>
       </c>
       <c r="J8" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>80</v>
       </c>
@@ -1667,13 +1747,13 @@
         <v>34</v>
       </c>
       <c r="J9" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" ht="39" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>85</v>
       </c>
@@ -1702,13 +1782,13 @@
         <v>55</v>
       </c>
       <c r="J10" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>89</v>
       </c>
@@ -1737,13 +1817,13 @@
         <v>34</v>
       </c>
       <c r="J11" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>93</v>
       </c>
@@ -1772,13 +1852,13 @@
         <v>55</v>
       </c>
       <c r="J12" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>97</v>
       </c>
@@ -1807,13 +1887,13 @@
         <v>55</v>
       </c>
       <c r="J13" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" ht="39" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>101</v>
       </c>
@@ -1842,13 +1922,13 @@
         <v>34</v>
       </c>
       <c r="J14" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>105</v>
       </c>
@@ -1877,13 +1957,13 @@
         <v>34</v>
       </c>
       <c r="J15" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:11" ht="39" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>109</v>
       </c>
@@ -1912,13 +1992,13 @@
         <v>34</v>
       </c>
       <c r="J16" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>113</v>
       </c>
@@ -1947,13 +2027,13 @@
         <v>55</v>
       </c>
       <c r="J17" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>117</v>
       </c>
@@ -1982,13 +2062,13 @@
         <v>34</v>
       </c>
       <c r="J18" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>122</v>
       </c>
@@ -2017,13 +2097,13 @@
         <v>34</v>
       </c>
       <c r="J19" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11" ht="52" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>126</v>
       </c>
@@ -2052,13 +2132,13 @@
         <v>34</v>
       </c>
       <c r="J20" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>130</v>
       </c>
@@ -2087,13 +2167,13 @@
         <v>34</v>
       </c>
       <c r="J21" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>134</v>
       </c>
@@ -2122,13 +2202,13 @@
         <v>55</v>
       </c>
       <c r="J22" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>138</v>
       </c>
@@ -2157,13 +2237,13 @@
         <v>34</v>
       </c>
       <c r="J23" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
@@ -2192,13 +2272,13 @@
         <v>34</v>
       </c>
       <c r="J24" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>147</v>
       </c>
@@ -2227,13 +2307,13 @@
         <v>55</v>
       </c>
       <c r="J25" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>152</v>
       </c>
@@ -2262,13 +2342,13 @@
         <v>34</v>
       </c>
       <c r="J26" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>156</v>
       </c>
@@ -2297,13 +2377,13 @@
         <v>34</v>
       </c>
       <c r="J27" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>160</v>
       </c>
@@ -2332,13 +2412,13 @@
         <v>34</v>
       </c>
       <c r="J28" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>164</v>
       </c>
@@ -2367,13 +2447,13 @@
         <v>55</v>
       </c>
       <c r="J29" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>168</v>
       </c>
@@ -2402,13 +2482,13 @@
         <v>55</v>
       </c>
       <c r="J30" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>172</v>
       </c>
@@ -2437,13 +2517,13 @@
         <v>34</v>
       </c>
       <c r="J31" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>177</v>
       </c>
@@ -2472,13 +2552,13 @@
         <v>34</v>
       </c>
       <c r="J32" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>181</v>
       </c>
@@ -2507,13 +2587,13 @@
         <v>34</v>
       </c>
       <c r="J33" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>185</v>
       </c>
@@ -2542,13 +2622,13 @@
         <v>34</v>
       </c>
       <c r="J34" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>189</v>
       </c>
@@ -2577,13 +2657,13 @@
         <v>34</v>
       </c>
       <c r="J35" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>193</v>
       </c>
@@ -2612,13 +2692,13 @@
         <v>55</v>
       </c>
       <c r="J36" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>197</v>
       </c>
@@ -2647,13 +2727,13 @@
         <v>34</v>
       </c>
       <c r="J37" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>201</v>
       </c>
@@ -2682,13 +2762,13 @@
         <v>34</v>
       </c>
       <c r="J38" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>205</v>
       </c>
@@ -2717,13 +2797,13 @@
         <v>34</v>
       </c>
       <c r="J39" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>209</v>
       </c>
@@ -2752,13 +2832,13 @@
         <v>55</v>
       </c>
       <c r="J40" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>213</v>
       </c>
@@ -2787,13 +2867,13 @@
         <v>55</v>
       </c>
       <c r="J41" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>217</v>
       </c>
@@ -2822,13 +2902,13 @@
         <v>55</v>
       </c>
       <c r="J42" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>223</v>
       </c>
@@ -2857,13 +2937,13 @@
         <v>55</v>
       </c>
       <c r="J43" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>227</v>
       </c>
@@ -2892,13 +2972,13 @@
         <v>55</v>
       </c>
       <c r="J44" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="K44" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>232</v>
       </c>
@@ -2920,20 +3000,20 @@
       <c r="G45" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="H45" s="13" t="s">
+      <c r="H45" s="9" t="s">
         <v>235</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>55</v>
       </c>
       <c r="J45" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="K45" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="9" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>236</v>
       </c>
@@ -2962,13 +3042,13 @@
         <v>55</v>
       </c>
       <c r="J46" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>241</v>
       </c>
@@ -2997,13 +3077,13 @@
         <v>55</v>
       </c>
       <c r="J47" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>245</v>
       </c>
@@ -3032,13 +3112,13 @@
         <v>55</v>
       </c>
       <c r="J48" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>249</v>
       </c>
@@ -3067,13 +3147,13 @@
         <v>55</v>
       </c>
       <c r="J49" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>253</v>
       </c>
@@ -3102,13 +3182,13 @@
         <v>34</v>
       </c>
       <c r="J50" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>257</v>
       </c>
@@ -3137,13 +3217,13 @@
         <v>55</v>
       </c>
       <c r="J51" s="9">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>261</v>
       </c>
@@ -3168,17 +3248,17 @@
       <c r="H52" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="12" t="s">
         <v>265</v>
       </c>
       <c r="J52" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>266</v>
       </c>
@@ -3207,128 +3287,128 @@
         <v>55</v>
       </c>
       <c r="J53" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>270</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="6" t="s">
         <v>272</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="F54" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="H54" s="6" t="s">
         <v>274</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>55</v>
       </c>
       <c r="J54" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="K54" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="16" t="s">
+    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
         <v>275</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="13" t="s">
+      <c r="F55" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="H55" s="13" t="s">
+      <c r="H55" s="9" t="s">
         <v>278</v>
       </c>
       <c r="I55" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J55" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="K55" s="13" t="s">
+      <c r="J55" s="9">
+        <v>3</v>
+      </c>
+      <c r="K55" s="9" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="15" t="s">
+    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>280</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="6" t="s">
         <v>283</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J56" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="K56" s="12" t="s">
+      <c r="J56" s="6">
+        <v>3</v>
+      </c>
+      <c r="K56" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="16" t="s">
+    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
         <v>284</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E57" s="9" t="s">
@@ -3337,33 +3417,33 @@
       <c r="F57" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="9" t="s">
         <v>287</v>
       </c>
       <c r="I57" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J57" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="K57" s="13" t="s">
+      <c r="J57" s="9">
+        <v>5</v>
+      </c>
+      <c r="K57" s="9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>288</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E58" s="6" t="s">
@@ -3372,986 +3452,1089 @@
       <c r="F58" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="6" t="s">
         <v>291</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J58" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="K58" s="12" t="s">
+      <c r="J58" s="6">
+        <v>3</v>
+      </c>
+      <c r="K58" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J59" s="14">
+        <v>5</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J60" s="15">
+        <v>5</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J61" s="14">
+        <v>3</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D62" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="34.0"/>
-    <col customWidth="1" min="3" max="5" width="14.0"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="6" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4368,7 +4551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -4376,16 +4559,16 @@
         <v>17</v>
       </c>
       <c r="C2" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
@@ -4393,16 +4576,16 @@
         <v>20</v>
       </c>
       <c r="C3" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
@@ -4410,16 +4593,16 @@
         <v>24</v>
       </c>
       <c r="C4" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
@@ -4427,16 +4610,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -4444,16 +4627,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>36</v>
       </c>
@@ -4461,16 +4644,16 @@
         <v>37</v>
       </c>
       <c r="C7" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
@@ -4478,16 +4661,16 @@
         <v>40</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
@@ -4495,16 +4678,16 @@
         <v>44</v>
       </c>
       <c r="C9" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
@@ -4512,16 +4695,16 @@
         <v>47</v>
       </c>
       <c r="C10" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>49</v>
       </c>
@@ -4529,1012 +4712,1010 @@
         <v>50</v>
       </c>
       <c r="C11" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
         <v>56</v>
       </c>
       <c r="C12" s="10">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D12" s="10">
-        <v>216.0</v>
+        <v>216</v>
       </c>
       <c r="E12" s="10"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>